--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N76_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N76_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>56.38483016724145</v>
+        <v>9.162534902176736</v>
       </c>
       <c r="D2" t="n">
-        <v>56.72304863484792</v>
+        <v>9.217495403162788</v>
       </c>
       <c r="E2" t="n">
-        <v>15.21514744240786</v>
+        <v>2.472461459391278</v>
       </c>
       <c r="F2" t="n">
-        <v>12.40422217333564</v>
+        <v>2.015686103167043</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>65.33725847833584</v>
+        <v>10.61730450272957</v>
       </c>
       <c r="D3" t="n">
-        <v>65.97831508833463</v>
+        <v>10.72147620185438</v>
       </c>
       <c r="E3" t="n">
-        <v>15.21514744240786</v>
+        <v>2.472461459391278</v>
       </c>
       <c r="F3" t="n">
-        <v>12.40422217333564</v>
+        <v>2.015686103167043</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>59.33102214633025</v>
+        <v>9.641291098778666</v>
       </c>
       <c r="D4" t="n">
-        <v>60.05031020136547</v>
+        <v>9.75817540772189</v>
       </c>
       <c r="E4" t="n">
-        <v>15.21514744240786</v>
+        <v>2.472461459391278</v>
       </c>
       <c r="F4" t="n">
-        <v>12.40422217333564</v>
+        <v>2.015686103167043</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.29702614343057</v>
+        <v>4.923266748307468</v>
       </c>
       <c r="D5" t="n">
-        <v>30.37277575910792</v>
+        <v>4.935576060855038</v>
       </c>
       <c r="E5" t="n">
-        <v>15.21514744240786</v>
+        <v>2.472461459391278</v>
       </c>
       <c r="F5" t="n">
-        <v>12.40422217333564</v>
+        <v>2.015686103167043</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>37.35826101818627</v>
+        <v>6.070717415455269</v>
       </c>
       <c r="D6" t="n">
-        <v>36.68514978231089</v>
+        <v>5.96133683962552</v>
       </c>
       <c r="E6" t="n">
-        <v>15.21514744240786</v>
+        <v>2.472461459391278</v>
       </c>
       <c r="F6" t="n">
-        <v>12.40422217333564</v>
+        <v>2.015686103167043</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.61626762420699</v>
+        <v>5.137643488933636</v>
       </c>
       <c r="D7" t="n">
-        <v>31.06663012964632</v>
+        <v>5.048327396067528</v>
       </c>
       <c r="E7" t="n">
-        <v>15.21514744240786</v>
+        <v>2.472461459391278</v>
       </c>
       <c r="F7" t="n">
-        <v>12.40422217333564</v>
+        <v>2.015686103167043</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>46.93819194059716</v>
+        <v>7.627456190347038</v>
       </c>
       <c r="D8" t="n">
-        <v>46.21415330665064</v>
+        <v>7.509799912330728</v>
       </c>
       <c r="E8" t="n">
-        <v>15.21514744240786</v>
+        <v>2.472461459391278</v>
       </c>
       <c r="F8" t="n">
-        <v>12.40422217333564</v>
+        <v>2.015686103167043</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>45.71141206234968</v>
+        <v>7.428104460131824</v>
       </c>
       <c r="D9" t="n">
-        <v>45.07187794600173</v>
+        <v>7.324180166225282</v>
       </c>
       <c r="E9" t="n">
-        <v>15.21514744240786</v>
+        <v>2.472461459391278</v>
       </c>
       <c r="F9" t="n">
-        <v>12.40422217333564</v>
+        <v>2.015686103167043</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>41.18912103117545</v>
+        <v>6.693232167566012</v>
       </c>
       <c r="D10" t="n">
-        <v>41.0672370737234</v>
+        <v>6.673426024480053</v>
       </c>
       <c r="E10" t="n">
-        <v>15.21514744240786</v>
+        <v>2.472461459391278</v>
       </c>
       <c r="F10" t="n">
-        <v>12.40422217333564</v>
+        <v>2.015686103167043</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>61.87696106807999</v>
+        <v>10.055006173563</v>
       </c>
       <c r="D11" t="n">
-        <v>61.16649311642344</v>
+        <v>9.939555131418809</v>
       </c>
       <c r="E11" t="n">
-        <v>15.21514744240786</v>
+        <v>2.472461459391278</v>
       </c>
       <c r="F11" t="n">
-        <v>12.40422217333564</v>
+        <v>2.015686103167043</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>9.21783840976507</v>
+        <v>1.497898741586824</v>
       </c>
       <c r="D12" t="n">
-        <v>66.50721588213341</v>
+        <v>10.80742258084668</v>
       </c>
       <c r="E12" t="n">
-        <v>15.21514744240786</v>
+        <v>2.472461459391278</v>
       </c>
       <c r="F12" t="n">
-        <v>12.40422217333564</v>
+        <v>2.015686103167043</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>44.74204600880922</v>
+        <v>7.270582476431498</v>
       </c>
       <c r="D13" t="n">
-        <v>53.32564193565202</v>
+        <v>8.665416814543454</v>
       </c>
       <c r="E13" t="n">
-        <v>15.21514744240786</v>
+        <v>2.472461459391278</v>
       </c>
       <c r="F13" t="n">
-        <v>12.40422217333564</v>
+        <v>2.015686103167043</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
